--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="固定特性" sheetId="2" r:id="rId1"/>
@@ -94,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -144,6 +149,9 @@
     <t>Des</t>
   </si>
   <si>
+    <t>max</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -249,6 +257,36 @@
     <t>爆伤</t>
   </si>
   <si>
+    <t>战卫</t>
+  </si>
+  <si>
+    <t>物伤</t>
+  </si>
+  <si>
+    <t>法灵</t>
+  </si>
+  <si>
+    <t>魔伤</t>
+  </si>
+  <si>
+    <t>道仆</t>
+  </si>
+  <si>
+    <t>道伤</t>
+  </si>
+  <si>
+    <t>破魂</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>神御</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
     <t>招财</t>
   </si>
   <si>
@@ -454,6 +492,60 @@
   </si>
   <si>
     <t>道伤加成，道伤增幅</t>
+  </si>
+  <si>
+    <t>强袭</t>
+  </si>
+  <si>
+    <t>2003,10003</t>
+  </si>
+  <si>
+    <t>攻击增幅，攻击倍率</t>
+  </si>
+  <si>
+    <t>固守</t>
+  </si>
+  <si>
+    <t>2002,10002</t>
+  </si>
+  <si>
+    <t>防御增幅，防御倍率</t>
+  </si>
+  <si>
+    <t>坚韧</t>
+  </si>
+  <si>
+    <t>2003,10001</t>
+  </si>
+  <si>
+    <t>生命增幅，生命倍率</t>
+  </si>
+  <si>
+    <t>战圣</t>
+  </si>
+  <si>
+    <t>1007,10007</t>
+  </si>
+  <si>
+    <t>物伤加成，物伤倍率</t>
+  </si>
+  <si>
+    <t>法神</t>
+  </si>
+  <si>
+    <t>1008,10008</t>
+  </si>
+  <si>
+    <t>魔伤加成，魔伤倍率</t>
+  </si>
+  <si>
+    <t>道尊</t>
+  </si>
+  <si>
+    <t>1009,10009</t>
+  </si>
+  <si>
+    <t>道伤加成，道伤倍率</t>
   </si>
 </sst>
 </file>
@@ -639,12 +731,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1114,12 +1206,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1441,7 +1533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Q107"/>
+  <dimension ref="C1:R112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1455,17 +1547,23 @@
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:17">
+    <row r="1" customHeight="1" spans="3:18">
       <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:17">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:18">
       <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1511,10 +1609,13 @@
       <c r="Q3" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1559,54 +1660,54 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1617,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
@@ -1635,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M19" si="0">L6*2</f>
+        <f t="shared" ref="M6:M24" si="0">L6*2</f>
         <v>6000</v>
       </c>
       <c r="N6" s="1">
@@ -1651,10 +1752,10 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1665,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -1683,7 +1784,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
@@ -1699,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1713,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1">
         <v>6</v>
@@ -1731,7 +1832,7 @@
         <v>3</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
@@ -1747,10 +1848,10 @@
         <v>10</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1761,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1">
         <v>6</v>
@@ -1779,7 +1880,7 @@
         <v>4</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
@@ -1795,10 +1896,10 @@
         <v>10</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1809,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <v>6</v>
@@ -1827,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1">
         <f t="shared" si="0"/>
@@ -1843,10 +1944,10 @@
         <v>10</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1857,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -1875,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" si="0"/>
@@ -1891,10 +1992,10 @@
         <v>10</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>10</v>
       </c>
@@ -1905,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1">
         <v>24</v>
@@ -1939,10 +2040,10 @@
         <v>10</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>11</v>
       </c>
@@ -1953,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1">
         <v>24</v>
@@ -1987,10 +2088,10 @@
         <v>10</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:17">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>12</v>
       </c>
@@ -2001,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>24</v>
@@ -2035,10 +2136,10 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>13</v>
       </c>
@@ -2049,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1">
         <v>24</v>
@@ -2083,10 +2184,10 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>14</v>
       </c>
@@ -2097,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="1">
         <v>24</v>
@@ -2131,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -2145,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -2179,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -2193,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="1">
         <v>24</v>
@@ -2227,7 +2328,7 @@
         <v>10</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -2241,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1">
         <v>24</v>
@@ -2275,27 +2376,117 @@
         <v>10</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E20" s="3"/>
+      <c r="C20" s="1">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="1">
+        <v>24</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>999</v>
+      </c>
+      <c r="J20" s="1">
+        <v>30</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1007</v>
+      </c>
+      <c r="L20" s="1">
+        <v>20</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1">
+        <v>6</v>
+      </c>
+      <c r="P20" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E21" s="3"/>
+      <c r="C21" s="1">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="1">
+        <v>24</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>999</v>
+      </c>
+      <c r="J21" s="1">
+        <v>30</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1008</v>
+      </c>
+      <c r="L21" s="1">
+        <v>20</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1">
+        <v>6</v>
+      </c>
+      <c r="P21" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C22" s="1">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G22" s="1">
         <v>24</v>
@@ -2307,34 +2498,34 @@
         <v>999</v>
       </c>
       <c r="J22" s="1">
+        <v>30</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1009</v>
+      </c>
+      <c r="L22" s="1">
         <v>20</v>
       </c>
-      <c r="K22" s="1">
-        <v>81</v>
-      </c>
-      <c r="L22" s="1">
-        <v>5</v>
-      </c>
       <c r="M22" s="1">
-        <f t="shared" ref="M22:M27" si="1">L22*2</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="N22" s="1">
         <v>1</v>
       </c>
       <c r="O22" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C23" s="1">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -2343,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G23" s="1">
         <v>24</v>
@@ -2355,34 +2546,34 @@
         <v>999</v>
       </c>
       <c r="J23" s="1">
+        <v>10</v>
+      </c>
+      <c r="K23" s="1">
+        <v>27</v>
+      </c>
+      <c r="L23" s="1">
+        <v>10</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="K23" s="1">
-        <v>82</v>
-      </c>
-      <c r="L23" s="1">
-        <v>5</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
       <c r="N23" s="1">
         <v>1</v>
       </c>
       <c r="O23" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P23" s="1">
         <v>10</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C24" s="1">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -2391,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G24" s="1">
         <v>24</v>
@@ -2403,225 +2594,360 @@
         <v>999</v>
       </c>
       <c r="J24" s="1">
+        <v>10</v>
+      </c>
+      <c r="K24" s="1">
+        <v>28</v>
+      </c>
+      <c r="L24" s="1">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="K24" s="1">
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1">
+        <v>6</v>
+      </c>
+      <c r="P24" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C27" s="1">
+        <v>81</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="1">
+        <v>24</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>999</v>
+      </c>
+      <c r="J27" s="1">
+        <v>20</v>
+      </c>
+      <c r="K27" s="1">
+        <v>81</v>
+      </c>
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" ref="M27:M32" si="1">L27*2</f>
+        <v>10</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
+        <v>3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C28" s="1">
+        <v>82</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="1">
+        <v>24</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>999</v>
+      </c>
+      <c r="J28" s="1">
+        <v>20</v>
+      </c>
+      <c r="K28" s="1">
+        <v>82</v>
+      </c>
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
+        <v>3</v>
+      </c>
+      <c r="P28" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C29" s="1">
         <v>83</v>
       </c>
-      <c r="L24" s="1">
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="1">
+        <v>24</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>999</v>
+      </c>
+      <c r="J29" s="1">
+        <v>20</v>
+      </c>
+      <c r="K29" s="1">
+        <v>83</v>
+      </c>
+      <c r="L29" s="1">
         <v>3</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M29" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N24" s="1">
-        <v>1</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
         <v>3</v>
       </c>
-      <c r="P24" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C25" s="1">
+      <c r="P29" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C30" s="1">
         <v>84</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="F30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="1">
         <v>24</v>
       </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1">
-        <v>999</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>999</v>
+      </c>
+      <c r="J30" s="1">
         <v>20</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K30" s="1">
         <v>84</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L30" s="1">
         <v>3</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M30" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N25" s="1">
-        <v>1</v>
-      </c>
-      <c r="O25" s="1">
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
         <v>3</v>
       </c>
-      <c r="P25" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C26" s="1">
+      <c r="P30" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C31" s="1">
         <v>85</v>
       </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="F31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="1">
         <v>24</v>
       </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>999</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
+        <v>999</v>
+      </c>
+      <c r="J31" s="1">
         <v>20</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K31" s="1">
         <v>85</v>
       </c>
-      <c r="L26" s="1">
-        <v>10</v>
-      </c>
-      <c r="M26" s="1">
+      <c r="L31" s="1">
+        <v>10</v>
+      </c>
+      <c r="M31" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="1">
-        <v>1</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1">
         <v>3</v>
       </c>
-      <c r="P26" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C27" s="1">
+      <c r="P31" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C32" s="1">
         <v>86</v>
       </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="F32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="1">
         <v>24</v>
       </c>
-      <c r="H27" s="1">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
-        <v>999</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>999</v>
+      </c>
+      <c r="J32" s="1">
         <v>20</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K32" s="1">
         <v>86</v>
       </c>
-      <c r="L27" s="1">
-        <v>10</v>
-      </c>
-      <c r="M27" s="1">
+      <c r="L32" s="1">
+        <v>10</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="1">
-        <v>1</v>
-      </c>
-      <c r="O27" s="1">
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
         <v>3</v>
       </c>
-      <c r="P27" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:17">
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:17">
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:17">
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:17">
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" customHeight="1" spans="5:5">
-      <c r="E33" s="3"/>
+      <c r="P32" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="5:5">
       <c r="E34" s="5"/>
     </row>
     <row r="35" customHeight="1" spans="5:5">
-      <c r="E35" s="6"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" customHeight="1" spans="5:5">
       <c r="E36" s="3"/>
     </row>
     <row r="37" customHeight="1" spans="5:5">
-      <c r="E37" s="3"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" customHeight="1" spans="5:5">
       <c r="E38" s="3"/>
     </row>
     <row r="39" customHeight="1" spans="5:5">
-      <c r="E39" s="3"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" customHeight="1" spans="5:5">
-      <c r="E40" s="3"/>
+      <c r="E40" s="5"/>
     </row>
     <row r="41" customHeight="1" spans="5:5">
-      <c r="E41" s="6"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" customHeight="1" spans="5:5">
-      <c r="E42" s="4"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" customHeight="1" spans="5:5">
       <c r="E43" s="3"/>
     </row>
     <row r="44" customHeight="1" spans="5:5">
-      <c r="E44" s="4"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" customHeight="1" spans="5:5">
       <c r="E45" s="3"/>
@@ -2630,25 +2956,25 @@
       <c r="E46" s="5"/>
     </row>
     <row r="47" customHeight="1" spans="5:5">
-      <c r="E47" s="4"/>
+      <c r="E47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="5:5">
       <c r="E48" s="3"/>
     </row>
     <row r="49" customHeight="1" spans="5:5">
-      <c r="E49" s="3"/>
+      <c r="E49" s="6"/>
     </row>
     <row r="50" customHeight="1" spans="5:5">
       <c r="E50" s="3"/>
     </row>
     <row r="51" customHeight="1" spans="5:5">
-      <c r="E51" s="5"/>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="5:5">
-      <c r="E52" s="3"/>
+      <c r="E52" s="6"/>
     </row>
     <row r="53" customHeight="1" spans="5:5">
-      <c r="E53" s="6"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" customHeight="1" spans="5:5">
       <c r="E54" s="3"/>
@@ -2657,16 +2983,16 @@
       <c r="E55" s="3"/>
     </row>
     <row r="56" customHeight="1" spans="5:5">
-      <c r="E56" s="3"/>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="5:5">
       <c r="E57" s="3"/>
     </row>
     <row r="58" customHeight="1" spans="5:5">
-      <c r="E58" s="3"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" customHeight="1" spans="5:5">
-      <c r="E59" s="6"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" customHeight="1" spans="5:5">
       <c r="E60" s="3"/>
@@ -2678,34 +3004,34 @@
       <c r="E62" s="3"/>
     </row>
     <row r="63" customHeight="1" spans="5:5">
-      <c r="E63" s="4"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" customHeight="1" spans="5:5">
-      <c r="E64" s="3"/>
+      <c r="E64" s="5"/>
     </row>
     <row r="65" customHeight="1" spans="5:5">
-      <c r="E65" s="6"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" customHeight="1" spans="5:5">
       <c r="E66" s="3"/>
     </row>
     <row r="67" customHeight="1" spans="5:5">
-      <c r="E67" s="5"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" customHeight="1" spans="5:5">
-      <c r="E68" s="3"/>
+      <c r="E68" s="6"/>
     </row>
     <row r="69" customHeight="1" spans="5:5">
       <c r="E69" s="3"/>
     </row>
     <row r="70" customHeight="1" spans="5:5">
-      <c r="E70" s="3"/>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" customHeight="1" spans="5:5">
-      <c r="E71" s="6"/>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" customHeight="1" spans="5:5">
-      <c r="E72" s="3"/>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" customHeight="1" spans="5:5">
       <c r="E73" s="3"/>
@@ -2717,28 +3043,43 @@
       <c r="E75" s="3"/>
     </row>
     <row r="76" customHeight="1" spans="5:5">
-      <c r="E76" s="4"/>
+      <c r="E76" s="5"/>
     </row>
     <row r="77" customHeight="1" spans="5:5">
-      <c r="E77" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="8:9">
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-    </row>
-    <row r="87" customHeight="1" spans="8:9">
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-    </row>
-    <row r="106" customHeight="1" spans="6:17">
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="Q106" s="7"/>
-    </row>
-    <row r="107" customHeight="1" spans="6:17">
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="Q107" s="7"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" customHeight="1" spans="5:5">
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" customHeight="1" spans="5:5">
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" customHeight="1" spans="5:5">
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" customHeight="1" spans="5:9">
+      <c r="E81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="5:9">
+      <c r="E82" s="5"/>
+    </row>
+    <row r="91" customHeight="1" spans="5:9">
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customHeight="1" spans="5:9">
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+    </row>
+    <row r="111" customHeight="1" spans="6:17">
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="Q111" s="7"/>
+    </row>
+    <row r="112" customHeight="1" spans="6:17">
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="Q112" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2755,7 +3096,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Q55"/>
+  <dimension ref="C1:R55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2770,17 +3111,23 @@
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:17">
+    <row r="1" customHeight="1" spans="3:18">
       <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:17">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:18">
       <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2826,10 +3173,13 @@
       <c r="Q3" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -2874,54 +3224,54 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2932,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -2947,16 +3297,16 @@
         <v>100</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -2965,10 +3315,10 @@
         <v>99</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2979,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2994,16 +3344,16 @@
         <v>100</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
@@ -3012,10 +3362,10 @@
         <v>99</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -3026,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -3041,16 +3391,16 @@
         <v>100</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O8" s="1">
         <v>1</v>
@@ -3059,10 +3409,10 @@
         <v>99</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -3073,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1">
         <v>36</v>
@@ -3088,16 +3438,16 @@
         <v>10</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
@@ -3106,10 +3456,10 @@
         <v>99</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -3120,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G10" s="1">
         <v>36</v>
@@ -3135,16 +3485,16 @@
         <v>10</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
@@ -3153,10 +3503,10 @@
         <v>99</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -3167,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G11" s="1">
         <v>24</v>
@@ -3182,16 +3532,16 @@
         <v>30</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -3200,10 +3550,10 @@
         <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -3214,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G12" s="1">
         <v>24</v>
@@ -3229,16 +3579,16 @@
         <v>50</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O12" s="1">
         <v>4</v>
@@ -3247,10 +3597,10 @@
         <v>99</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -3261,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G13" s="1">
         <v>24</v>
@@ -3276,16 +3626,16 @@
         <v>50</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O13" s="1">
         <v>4</v>
@@ -3294,10 +3644,10 @@
         <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3308,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G14" s="1">
         <v>24</v>
@@ -3323,16 +3673,16 @@
         <v>25</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O14" s="1">
         <v>4</v>
@@ -3341,10 +3691,10 @@
         <v>99</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3355,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G15" s="1">
         <v>24</v>
@@ -3370,16 +3720,16 @@
         <v>50</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -3388,10 +3738,10 @@
         <v>99</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3402,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G16" s="1">
         <v>24</v>
@@ -3417,16 +3767,16 @@
         <v>50</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O16" s="1">
         <v>1</v>
@@ -3435,7 +3785,7 @@
         <v>99</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3449,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -3464,16 +3814,16 @@
         <v>10</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
@@ -3482,7 +3832,7 @@
         <v>99</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3496,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G18" s="1">
         <v>9</v>
@@ -3511,16 +3861,16 @@
         <v>100</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O18" s="1">
         <v>4</v>
@@ -3529,7 +3879,7 @@
         <v>99</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3543,7 +3893,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G19" s="1">
         <v>9</v>
@@ -3558,16 +3908,16 @@
         <v>100</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O19" s="1">
         <v>4</v>
@@ -3576,7 +3926,7 @@
         <v>99</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3590,7 +3940,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -3605,16 +3955,16 @@
         <v>100</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -3623,26 +3973,290 @@
         <v>99</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E21" s="3"/>
+      <c r="C21" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="1">
+        <v>24</v>
+      </c>
+      <c r="H21" s="1">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>999</v>
+      </c>
+      <c r="J21" s="1">
+        <v>50</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="1">
+        <v>6</v>
+      </c>
+      <c r="P21" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E22" s="4"/>
+      <c r="C22" s="1">
+        <v>1017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" s="1">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>999</v>
+      </c>
+      <c r="J22" s="1">
+        <v>50</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O22" s="1">
+        <v>6</v>
+      </c>
+      <c r="P22" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E23" s="3"/>
+      <c r="C23" s="1">
+        <v>1018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="1">
+        <v>24</v>
+      </c>
+      <c r="H23" s="1">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <v>999</v>
+      </c>
+      <c r="J23" s="1">
+        <v>50</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" s="1">
+        <v>6</v>
+      </c>
+      <c r="P23" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E24" s="5"/>
+      <c r="C24" s="1">
+        <v>1019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" s="1">
+        <v>24</v>
+      </c>
+      <c r="H24" s="1">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1">
+        <v>999</v>
+      </c>
+      <c r="J24" s="1">
+        <v>50</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O24" s="1">
+        <v>6</v>
+      </c>
+      <c r="P24" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E25" s="4"/>
+      <c r="C25" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="1">
+        <v>24</v>
+      </c>
+      <c r="H25" s="1">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
+        <v>999</v>
+      </c>
+      <c r="J25" s="1">
+        <v>50</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O25" s="1">
+        <v>6</v>
+      </c>
+      <c r="P25" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E26" s="3"/>
+      <c r="C26" s="1">
+        <v>1021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="1">
+        <v>24</v>
+      </c>
+      <c r="H26" s="1">
+        <v>13</v>
+      </c>
+      <c r="I26" s="1">
+        <v>999</v>
+      </c>
+      <c r="J26" s="1">
+        <v>50</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O26" s="1">
+        <v>6</v>
+      </c>
+      <c r="P26" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="E27" s="3"/>
@@ -3651,13 +4265,13 @@
       <c r="E28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E29" s="5"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="E30" s="3"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
-      <c r="E31" s="6"/>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="E32" s="3"/>
@@ -3675,7 +4289,7 @@
       <c r="E36" s="3"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E37" s="6"/>
+      <c r="E37" s="5"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="5:5">
       <c r="E38" s="3"/>
@@ -3687,19 +4301,19 @@
       <c r="E40" s="3"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E41" s="4"/>
+      <c r="E41" s="6"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="5:5">
       <c r="E42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E43" s="6"/>
+      <c r="E43" s="5"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="5:5">
       <c r="E44" s="3"/>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E45" s="5"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="5:5">
       <c r="E46" s="3"/>
@@ -3711,7 +4325,7 @@
       <c r="E48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E49" s="6"/>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="5:5">
       <c r="E50" s="3"/>
@@ -3726,10 +4340,10 @@
       <c r="E53" s="3"/>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E54" s="4"/>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E55" s="6"/>
+      <c r="E55" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -731,12 +731,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1533,7 +1533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:R112"/>
+  <dimension ref="C1:S112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1544,26 +1544,33 @@
     <col min="13" max="14" width="11.5833333333333" style="1" customWidth="1"/>
     <col min="15" max="16" width="9" style="1"/>
     <col min="17" max="17" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="18" max="18" width="14.75" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:18">
+    <row r="1" customHeight="1" spans="3:19">
       <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:18">
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:19">
       <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1613,7 +1620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1660,7 +1667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1707,7 +1714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1754,8 +1761,15 @@
       <c r="Q6" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R6" s="1">
+        <f t="shared" ref="R6:R32" si="1">INT((S6-H6)/G6)+1</f>
+        <v>13</v>
+      </c>
+      <c r="S6" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1802,8 +1816,15 @@
       <c r="Q7" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R7" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S7" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1850,8 +1871,15 @@
       <c r="Q8" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R8" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S8" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1898,8 +1926,15 @@
       <c r="Q9" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R9" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S9" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1946,8 +1981,15 @@
       <c r="Q10" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R10" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S10" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1994,8 +2036,15 @@
       <c r="Q11" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R11" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S11" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C12" s="1">
         <v>10</v>
       </c>
@@ -2042,8 +2091,15 @@
       <c r="Q12" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R12" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S12" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C13" s="1">
         <v>11</v>
       </c>
@@ -2090,8 +2146,15 @@
       <c r="Q13" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:18">
+      <c r="R13" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S13" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:19">
       <c r="C14" s="1">
         <v>12</v>
       </c>
@@ -2138,8 +2201,15 @@
       <c r="Q14" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R14" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S14" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C15" s="1">
         <v>13</v>
       </c>
@@ -2186,8 +2256,15 @@
       <c r="Q15" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R15" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S15" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C16" s="1">
         <v>14</v>
       </c>
@@ -2234,8 +2311,15 @@
       <c r="Q16" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R16" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S16" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C17" s="1">
         <v>15</v>
       </c>
@@ -2282,8 +2366,15 @@
       <c r="Q17" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R17" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S17" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C18" s="1">
         <v>21</v>
       </c>
@@ -2330,8 +2421,15 @@
       <c r="Q18" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R18" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S18" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C19" s="1">
         <v>22</v>
       </c>
@@ -2378,8 +2476,15 @@
       <c r="Q19" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R19" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S19" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C20" s="1">
         <v>23</v>
       </c>
@@ -2426,8 +2531,15 @@
       <c r="Q20" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R20" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S20" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C21" s="1">
         <v>24</v>
       </c>
@@ -2474,8 +2586,15 @@
       <c r="Q21" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R21" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S21" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C22" s="1">
         <v>25</v>
       </c>
@@ -2522,8 +2641,15 @@
       <c r="Q22" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R22" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S22" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C23" s="1">
         <v>26</v>
       </c>
@@ -2570,8 +2696,15 @@
       <c r="Q23" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R23" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S23" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C24" s="1">
         <v>27</v>
       </c>
@@ -2618,14 +2751,21 @@
       <c r="Q24" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R24" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S24" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E25" s="3"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E26" s="3"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C27" s="1">
         <v>81</v>
       </c>
@@ -2657,7 +2797,7 @@
         <v>5</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" ref="M27:M32" si="1">L27*2</f>
+        <f t="shared" ref="M27:M32" si="2">L27*2</f>
         <v>10</v>
       </c>
       <c r="N27" s="1">
@@ -2672,8 +2812,15 @@
       <c r="Q27" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R27" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S27" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C28" s="1">
         <v>82</v>
       </c>
@@ -2705,7 +2852,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N28" s="1">
@@ -2720,8 +2867,15 @@
       <c r="Q28" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R28" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S28" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C29" s="1">
         <v>83</v>
       </c>
@@ -2753,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N29" s="1">
@@ -2768,8 +2922,15 @@
       <c r="Q29" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R29" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S29" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C30" s="1">
         <v>84</v>
       </c>
@@ -2801,7 +2962,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N30" s="1">
@@ -2816,8 +2977,15 @@
       <c r="Q30" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R30" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S30" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C31" s="1">
         <v>85</v>
       </c>
@@ -2849,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N31" s="1">
@@ -2864,8 +3032,15 @@
       <c r="Q31" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R31" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S31" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C32" s="1">
         <v>86</v>
       </c>
@@ -2897,7 +3072,7 @@
         <v>10</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N32" s="1">
@@ -2910,6 +3085,13 @@
         <v>10</v>
       </c>
       <c r="Q32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R32" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S32" s="1">
         <v>73</v>
       </c>
     </row>
@@ -3096,7 +3278,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:R55"/>
+  <dimension ref="C1:S55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3108,26 +3290,33 @@
     <col min="14" max="15" width="13.8333333333333" style="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="23.5833333333333" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="18" max="18" width="14.75" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:18">
+    <row r="1" customHeight="1" spans="3:19">
       <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:18">
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:19">
       <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3177,7 +3366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
@@ -3224,7 +3413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
@@ -3271,7 +3460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -3317,8 +3506,15 @@
       <c r="Q6" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R6" s="1">
+        <f t="shared" ref="R6:R26" si="0">INT((S6-H6)/G6)+1</f>
+        <v>9</v>
+      </c>
+      <c r="S6" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -3364,8 +3560,15 @@
       <c r="Q7" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R7" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="S7" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -3411,8 +3614,15 @@
       <c r="Q8" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R8" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="S8" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -3458,8 +3668,15 @@
       <c r="Q9" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R9" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S9" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -3505,8 +3722,15 @@
       <c r="Q10" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R10" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S10" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -3552,8 +3776,15 @@
       <c r="Q11" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R11" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S11" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -3599,8 +3830,15 @@
       <c r="Q12" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R12" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S12" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -3646,8 +3884,15 @@
       <c r="Q13" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R13" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S13" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3693,8 +3938,15 @@
       <c r="Q14" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R14" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S14" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3740,8 +3992,15 @@
       <c r="Q15" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R15" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S15" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3787,8 +4046,15 @@
       <c r="Q16" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R16" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S16" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -3834,8 +4100,15 @@
       <c r="Q17" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="R17" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S17" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16" customHeight="1" spans="3:19">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
@@ -3881,8 +4154,15 @@
       <c r="Q18" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="R18" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="S18" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16" customHeight="1" spans="3:19">
       <c r="C19" s="1">
         <v>1014</v>
       </c>
@@ -3928,8 +4208,15 @@
       <c r="Q19" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="R19" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="S19" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="16" customHeight="1" spans="3:19">
       <c r="C20" s="1">
         <v>1015</v>
       </c>
@@ -3975,8 +4262,15 @@
       <c r="Q20" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R20" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="S20" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
@@ -4022,8 +4316,15 @@
       <c r="Q21" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R21" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S21" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C22" s="1">
         <v>1017</v>
       </c>
@@ -4069,8 +4370,15 @@
       <c r="Q22" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R22" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S22" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C23" s="1">
         <v>1018</v>
       </c>
@@ -4116,8 +4424,15 @@
       <c r="Q23" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R23" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S23" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C24" s="1">
         <v>1019</v>
       </c>
@@ -4163,8 +4478,15 @@
       <c r="Q24" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R24" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S24" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C25" s="1">
         <v>1020</v>
       </c>
@@ -4210,8 +4532,15 @@
       <c r="Q25" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R25" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S25" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
@@ -4257,23 +4586,30 @@
       <c r="Q26" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="R26" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S26" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E27" s="3"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E28" s="3"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E30" s="3"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E31" s="5"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="E32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="5:5">

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -287,6 +287,24 @@
     <t>减伤</t>
   </si>
   <si>
+    <t>战神</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>法神</t>
+  </si>
+  <si>
+    <t>法攻倍率</t>
+  </si>
+  <si>
+    <t>道神</t>
+  </si>
+  <si>
+    <t>道攻倍率</t>
+  </si>
+  <si>
     <t>招财</t>
   </si>
   <si>
@@ -528,9 +546,6 @@
   </si>
   <si>
     <t>物伤加成，物伤倍率</t>
-  </si>
-  <si>
-    <t>法神</t>
   </si>
   <si>
     <t>1008,10008</t>
@@ -1533,7 +1548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:S112"/>
+  <dimension ref="C1:S115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1746,7 +1761,7 @@
         <v>22</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M24" si="0">L6*2</f>
+        <f t="shared" ref="M6:M27" si="0">L6*2</f>
         <v>6000</v>
       </c>
       <c r="N6" s="1">
@@ -2058,7 +2073,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="1">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -2093,7 +2108,7 @@
       </c>
       <c r="R12" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S12" s="1">
         <v>73</v>
@@ -2113,7 +2128,7 @@
         <v>38</v>
       </c>
       <c r="G13" s="1">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
@@ -2148,7 +2163,7 @@
       </c>
       <c r="R13" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13" s="1">
         <v>73</v>
@@ -2168,7 +2183,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -2203,7 +2218,7 @@
       </c>
       <c r="R14" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S14" s="1">
         <v>73</v>
@@ -2672,7 +2687,7 @@
         <v>999</v>
       </c>
       <c r="J23" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1">
         <v>27</v>
@@ -2727,7 +2742,7 @@
         <v>999</v>
       </c>
       <c r="J24" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K24" s="1">
         <v>28</v>
@@ -2760,14 +2775,118 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="E25" s="3"/>
+      <c r="C25" s="1">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="1">
+        <v>36</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>999</v>
+      </c>
+      <c r="J25" s="1">
+        <v>5</v>
+      </c>
+      <c r="K25" s="1">
+        <v>10004</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1">
+        <v>6</v>
+      </c>
+      <c r="P25" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R25" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S25" s="1">
+        <v>73</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="E26" s="3"/>
+      <c r="C26" s="1">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="1">
+        <v>36</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>999</v>
+      </c>
+      <c r="J26" s="1">
+        <v>5</v>
+      </c>
+      <c r="K26" s="1">
+        <v>10005</v>
+      </c>
+      <c r="L26" s="1">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1">
+        <v>6</v>
+      </c>
+      <c r="P26" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R26" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S26" s="1">
+        <v>73</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C27" s="1">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -2776,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G27" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
@@ -2788,369 +2907,421 @@
         <v>999</v>
       </c>
       <c r="J27" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K27" s="1">
-        <v>81</v>
+        <v>10006</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" ref="M27:M32" si="2">L27*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N27" s="1">
         <v>1</v>
       </c>
       <c r="O27" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P27" s="1">
         <v>10</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S27" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C30" s="1">
+        <v>81</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="1">
+        <v>24</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>999</v>
+      </c>
+      <c r="J30" s="1">
+        <v>10</v>
+      </c>
+      <c r="K30" s="1">
+        <v>81</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" ref="M30:M35" si="2">L30*2</f>
+        <v>10</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
+        <v>3</v>
+      </c>
+      <c r="P30" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" ref="R30:R35" si="3">INT((S30-H30)/G30)+1</f>
         <v>4</v>
       </c>
-      <c r="S27" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C28" s="1">
+      <c r="S30" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C31" s="1">
         <v>82</v>
       </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" s="1">
+      <c r="F31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="1">
         <v>24</v>
       </c>
-      <c r="H28" s="1">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
         <v>999</v>
       </c>
-      <c r="J28" s="1">
-        <v>20</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="J31" s="1">
+        <v>10</v>
+      </c>
+      <c r="K31" s="1">
         <v>82</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L31" s="1">
         <v>5</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M31" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N28" s="1">
-        <v>1</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1">
         <v>3</v>
       </c>
-      <c r="P28" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="R28" s="1">
-        <f t="shared" si="1"/>
+      <c r="P31" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S28" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C29" s="1">
+      <c r="S31" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C32" s="1">
         <v>83</v>
       </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="F32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="1">
         <v>24</v>
       </c>
-      <c r="H29" s="1">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
         <v>999</v>
       </c>
-      <c r="J29" s="1">
-        <v>20</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="J32" s="1">
+        <v>10</v>
+      </c>
+      <c r="K32" s="1">
         <v>83</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L32" s="1">
         <v>3</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M32" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="N29" s="1">
-        <v>1</v>
-      </c>
-      <c r="O29" s="1">
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
         <v>3</v>
       </c>
-      <c r="P29" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="R29" s="1">
-        <f t="shared" si="1"/>
+      <c r="P32" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R32" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S29" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C30" s="1">
+      <c r="S32" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C33" s="1">
         <v>84</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="1">
         <v>24</v>
       </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
         <v>999</v>
       </c>
-      <c r="J30" s="1">
-        <v>20</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="J33" s="1">
+        <v>10</v>
+      </c>
+      <c r="K33" s="1">
         <v>84</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L33" s="1">
         <v>3</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M33" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="N30" s="1">
-        <v>1</v>
-      </c>
-      <c r="O30" s="1">
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1">
         <v>3</v>
       </c>
-      <c r="P30" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R30" s="1">
-        <f t="shared" si="1"/>
+      <c r="P33" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R33" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S30" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C31" s="1">
+      <c r="S33" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C34" s="1">
         <v>85</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="1">
+      <c r="F34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="1">
         <v>24</v>
       </c>
-      <c r="H31" s="1">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
         <v>999</v>
       </c>
-      <c r="J31" s="1">
-        <v>20</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="J34" s="1">
+        <v>10</v>
+      </c>
+      <c r="K34" s="1">
         <v>85</v>
       </c>
-      <c r="L31" s="1">
-        <v>10</v>
-      </c>
-      <c r="M31" s="1">
+      <c r="L34" s="1">
+        <v>10</v>
+      </c>
+      <c r="M34" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-      <c r="O31" s="1">
+      <c r="N34" s="1">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1">
         <v>3</v>
       </c>
-      <c r="P31" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R31" s="1">
-        <f t="shared" si="1"/>
+      <c r="P34" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R34" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S31" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C32" s="1">
+      <c r="S34" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C35" s="1">
         <v>86</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" s="1">
         <v>24</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
         <v>999</v>
       </c>
-      <c r="J32" s="1">
-        <v>20</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="J35" s="1">
+        <v>10</v>
+      </c>
+      <c r="K35" s="1">
         <v>86</v>
       </c>
-      <c r="L32" s="1">
-        <v>10</v>
-      </c>
-      <c r="M32" s="1">
+      <c r="L35" s="1">
+        <v>10</v>
+      </c>
+      <c r="M35" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N32" s="1">
-        <v>1</v>
-      </c>
-      <c r="O32" s="1">
+      <c r="N35" s="1">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1">
         <v>3</v>
       </c>
-      <c r="P32" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R32" s="1">
-        <f t="shared" si="1"/>
+      <c r="P35" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R35" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S32" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="5:5">
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" customHeight="1" spans="5:5">
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="5:5">
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" customHeight="1" spans="5:5">
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="5:5">
+      <c r="S35" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:19">
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:19">
       <c r="E38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="5:5">
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="5:5">
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" customHeight="1" spans="5:5">
+    <row r="39" customHeight="1" spans="3:19">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:19">
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:19">
       <c r="E41" s="3"/>
     </row>
-    <row r="42" customHeight="1" spans="5:5">
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" customHeight="1" spans="5:5">
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" customHeight="1" spans="5:5">
+    <row r="42" customHeight="1" spans="3:19">
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="3:19">
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:19">
       <c r="E44" s="3"/>
     </row>
-    <row r="45" customHeight="1" spans="5:5">
+    <row r="45" customHeight="1" spans="3:19">
       <c r="E45" s="3"/>
     </row>
-    <row r="46" customHeight="1" spans="5:5">
-      <c r="E46" s="5"/>
-    </row>
-    <row r="47" customHeight="1" spans="5:5">
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="5:5">
+    <row r="46" customHeight="1" spans="3:19">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:19">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" customHeight="1" spans="3:19">
       <c r="E48" s="3"/>
     </row>
     <row r="49" customHeight="1" spans="5:5">
-      <c r="E49" s="6"/>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" customHeight="1" spans="5:5">
-      <c r="E50" s="3"/>
+      <c r="E50" s="6"/>
     </row>
     <row r="51" customHeight="1" spans="5:5">
-      <c r="E51" s="4"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" customHeight="1" spans="5:5">
       <c r="E52" s="6"/>
@@ -3159,28 +3330,28 @@
       <c r="E53" s="3"/>
     </row>
     <row r="54" customHeight="1" spans="5:5">
-      <c r="E54" s="3"/>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" customHeight="1" spans="5:5">
-      <c r="E55" s="3"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" customHeight="1" spans="5:5">
-      <c r="E56" s="4"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" customHeight="1" spans="5:5">
       <c r="E57" s="3"/>
     </row>
     <row r="58" customHeight="1" spans="5:5">
-      <c r="E58" s="5"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" customHeight="1" spans="5:5">
-      <c r="E59" s="3"/>
+      <c r="E59" s="4"/>
     </row>
     <row r="60" customHeight="1" spans="5:5">
       <c r="E60" s="3"/>
     </row>
     <row r="61" customHeight="1" spans="5:5">
-      <c r="E61" s="3"/>
+      <c r="E61" s="5"/>
     </row>
     <row r="62" customHeight="1" spans="5:5">
       <c r="E62" s="3"/>
@@ -3189,7 +3360,7 @@
       <c r="E63" s="3"/>
     </row>
     <row r="64" customHeight="1" spans="5:5">
-      <c r="E64" s="5"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" customHeight="1" spans="5:5">
       <c r="E65" s="3"/>
@@ -3198,34 +3369,34 @@
       <c r="E66" s="3"/>
     </row>
     <row r="67" customHeight="1" spans="5:5">
-      <c r="E67" s="3"/>
+      <c r="E67" s="5"/>
     </row>
     <row r="68" customHeight="1" spans="5:5">
-      <c r="E68" s="6"/>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" customHeight="1" spans="5:5">
       <c r="E69" s="3"/>
     </row>
     <row r="70" customHeight="1" spans="5:5">
-      <c r="E70" s="5"/>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" customHeight="1" spans="5:5">
-      <c r="E71" s="3"/>
+      <c r="E71" s="6"/>
     </row>
     <row r="72" customHeight="1" spans="5:5">
-      <c r="E72" s="4"/>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" customHeight="1" spans="5:5">
-      <c r="E73" s="3"/>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" customHeight="1" spans="5:5">
       <c r="E74" s="3"/>
     </row>
     <row r="75" customHeight="1" spans="5:5">
-      <c r="E75" s="3"/>
+      <c r="E75" s="4"/>
     </row>
     <row r="76" customHeight="1" spans="5:5">
-      <c r="E76" s="5"/>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" customHeight="1" spans="5:5">
       <c r="E77" s="3"/>
@@ -3234,34 +3405,43 @@
       <c r="E78" s="3"/>
     </row>
     <row r="79" customHeight="1" spans="5:5">
-      <c r="E79" s="3"/>
+      <c r="E79" s="5"/>
     </row>
     <row r="80" customHeight="1" spans="5:5">
       <c r="E80" s="3"/>
     </row>
     <row r="81" customHeight="1" spans="5:9">
-      <c r="E81" s="6"/>
+      <c r="E81" s="3"/>
     </row>
     <row r="82" customHeight="1" spans="5:9">
-      <c r="E82" s="5"/>
-    </row>
-    <row r="91" customHeight="1" spans="5:9">
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-    </row>
-    <row r="92" customHeight="1" spans="5:9">
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-    </row>
-    <row r="111" customHeight="1" spans="6:17">
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="Q111" s="7"/>
-    </row>
-    <row r="112" customHeight="1" spans="6:17">
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="Q112" s="7"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" customHeight="1" spans="5:9">
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" customHeight="1" spans="5:9">
+      <c r="E84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="5:9">
+      <c r="E85" s="5"/>
+    </row>
+    <row r="94" customHeight="1" spans="5:9">
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customHeight="1" spans="5:9">
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+    </row>
+    <row r="114" customHeight="1" spans="6:17">
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="Q114" s="7"/>
+    </row>
+    <row r="115" customHeight="1" spans="6:17">
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="Q115" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3471,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -3486,16 +3666,16 @@
         <v>100</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -3504,7 +3684,7 @@
         <v>99</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ref="R6:R26" si="0">INT((S6-H6)/G6)+1</f>
@@ -3525,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -3540,16 +3720,16 @@
         <v>100</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
@@ -3558,7 +3738,7 @@
         <v>99</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="0"/>
@@ -3579,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -3594,16 +3774,16 @@
         <v>100</v>
       </c>
       <c r="K8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="O8" s="1">
         <v>1</v>
@@ -3612,7 +3792,7 @@
         <v>99</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="0"/>
@@ -3633,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G9" s="1">
         <v>36</v>
@@ -3648,16 +3828,16 @@
         <v>10</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
@@ -3666,7 +3846,7 @@
         <v>99</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" si="0"/>
@@ -3687,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G10" s="1">
         <v>36</v>
@@ -3702,16 +3882,16 @@
         <v>10</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
@@ -3720,7 +3900,7 @@
         <v>99</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="0"/>
@@ -3741,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G11" s="1">
         <v>24</v>
@@ -3756,16 +3936,16 @@
         <v>30</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -3774,7 +3954,7 @@
         <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="0"/>
@@ -3795,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G12" s="1">
         <v>24</v>
@@ -3810,16 +3990,16 @@
         <v>50</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O12" s="1">
         <v>4</v>
@@ -3828,7 +4008,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="0"/>
@@ -3849,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G13" s="1">
         <v>24</v>
@@ -3864,16 +4044,16 @@
         <v>50</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O13" s="1">
         <v>4</v>
@@ -3882,7 +4062,7 @@
         <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="0"/>
@@ -3903,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G14" s="1">
         <v>24</v>
@@ -3918,16 +4098,16 @@
         <v>25</v>
       </c>
       <c r="K14" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="N14" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O14" s="1">
         <v>4</v>
@@ -3936,7 +4116,7 @@
         <v>99</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="0"/>
@@ -3957,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G15" s="1">
         <v>24</v>
@@ -3972,16 +4152,16 @@
         <v>50</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -3990,7 +4170,7 @@
         <v>99</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="0"/>
@@ -4011,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G16" s="1">
         <v>24</v>
@@ -4026,16 +4206,16 @@
         <v>50</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O16" s="1">
         <v>1</v>
@@ -4044,7 +4224,7 @@
         <v>99</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="0"/>
@@ -4065,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -4080,16 +4260,16 @@
         <v>10</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
@@ -4098,7 +4278,7 @@
         <v>99</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" si="0"/>
@@ -4119,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1">
         <v>9</v>
@@ -4134,16 +4314,16 @@
         <v>100</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O18" s="1">
         <v>4</v>
@@ -4152,7 +4332,7 @@
         <v>99</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" si="0"/>
@@ -4173,7 +4353,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1">
         <v>9</v>
@@ -4188,16 +4368,16 @@
         <v>100</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O19" s="1">
         <v>4</v>
@@ -4206,7 +4386,7 @@
         <v>99</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" si="0"/>
@@ -4227,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -4242,16 +4422,16 @@
         <v>100</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -4260,7 +4440,7 @@
         <v>99</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" si="0"/>
@@ -4281,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G21" s="1">
         <v>24</v>
@@ -4296,16 +4476,16 @@
         <v>50</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O21" s="1">
         <v>6</v>
@@ -4314,7 +4494,7 @@
         <v>99</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" si="0"/>
@@ -4335,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G22" s="1">
         <v>24</v>
@@ -4350,16 +4530,16 @@
         <v>50</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O22" s="1">
         <v>6</v>
@@ -4368,7 +4548,7 @@
         <v>99</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" si="0"/>
@@ -4389,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G23" s="1">
         <v>24</v>
@@ -4404,16 +4584,16 @@
         <v>50</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O23" s="1">
         <v>6</v>
@@ -4422,7 +4602,7 @@
         <v>99</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" si="0"/>
@@ -4443,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G24" s="1">
         <v>24</v>
@@ -4458,16 +4638,16 @@
         <v>50</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O24" s="1">
         <v>6</v>
@@ -4476,7 +4656,7 @@
         <v>99</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" si="0"/>
@@ -4497,7 +4677,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
@@ -4512,16 +4692,16 @@
         <v>50</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O25" s="1">
         <v>6</v>
@@ -4530,7 +4710,7 @@
         <v>99</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" si="0"/>
@@ -4551,7 +4731,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G26" s="1">
         <v>24</v>
@@ -4566,16 +4746,16 @@
         <v>50</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O26" s="1">
         <v>6</v>
@@ -4584,7 +4764,7 @@
         <v>99</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" si="0"/>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -305,6 +305,24 @@
     <t>道攻倍率</t>
   </si>
   <si>
+    <t>生机</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>不屈</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>固守</t>
+  </si>
+  <si>
+    <t>减伤倍率</t>
+  </si>
+  <si>
     <t>招财</t>
   </si>
   <si>
@@ -519,9 +537,6 @@
   </si>
   <si>
     <t>攻击增幅，攻击倍率</t>
-  </si>
-  <si>
-    <t>固守</t>
   </si>
   <si>
     <t>2002,10002</t>
@@ -1548,7 +1563,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:S115"/>
+  <dimension ref="C1:S118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1761,7 +1776,7 @@
         <v>22</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M27" si="0">L6*2</f>
+        <f t="shared" ref="M6:M30" si="0">L6*2</f>
         <v>6000</v>
       </c>
       <c r="N6" s="1">
@@ -2940,14 +2955,118 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="E28" s="3"/>
+      <c r="C28" s="1">
+        <v>31</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="1">
+        <v>36</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>999</v>
+      </c>
+      <c r="J28" s="1">
+        <v>5</v>
+      </c>
+      <c r="K28" s="1">
+        <v>10001</v>
+      </c>
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
+        <v>6</v>
+      </c>
+      <c r="P28" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R28" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S28" s="1">
+        <v>73</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="E29" s="3"/>
+      <c r="C29" s="1">
+        <v>32</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="1">
+        <v>36</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>999</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5</v>
+      </c>
+      <c r="K29" s="1">
+        <v>10002</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <v>6</v>
+      </c>
+      <c r="P29" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S29" s="1">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C30" s="1">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -2956,10 +3075,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G30" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -2968,151 +3087,47 @@
         <v>999</v>
       </c>
       <c r="J30" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K30" s="1">
-        <v>81</v>
+        <v>10028</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" ref="M30:M35" si="2">L30*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N30" s="1">
         <v>1</v>
       </c>
       <c r="O30" s="1">
+        <v>6</v>
+      </c>
+      <c r="P30" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="P30" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R30" s="1">
-        <f t="shared" ref="R30:R35" si="3">INT((S30-H30)/G30)+1</f>
-        <v>4</v>
-      </c>
       <c r="S30" s="1">
         <v>73</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C31" s="1">
-        <v>82</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="1">
-        <v>24</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
-        <v>999</v>
-      </c>
-      <c r="J31" s="1">
-        <v>10</v>
-      </c>
-      <c r="K31" s="1">
-        <v>82</v>
-      </c>
-      <c r="L31" s="1">
-        <v>5</v>
-      </c>
-      <c r="M31" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-      <c r="O31" s="1">
-        <v>3</v>
-      </c>
-      <c r="P31" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R31" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="S31" s="1">
-        <v>73</v>
-      </c>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C32" s="1">
-        <v>83</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" s="1">
-        <v>24</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>999</v>
-      </c>
-      <c r="J32" s="1">
-        <v>10</v>
-      </c>
-      <c r="K32" s="1">
-        <v>83</v>
-      </c>
-      <c r="L32" s="1">
-        <v>3</v>
-      </c>
-      <c r="M32" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="N32" s="1">
-        <v>1</v>
-      </c>
-      <c r="O32" s="1">
-        <v>3</v>
-      </c>
-      <c r="P32" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R32" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="S32" s="1">
-        <v>73</v>
-      </c>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C33" s="1">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
@@ -3136,14 +3151,14 @@
         <v>10</v>
       </c>
       <c r="K33" s="1">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L33" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f t="shared" ref="M33:M38" si="2">L33*2</f>
+        <v>10</v>
       </c>
       <c r="N33" s="1">
         <v>1</v>
@@ -3158,7 +3173,7 @@
         <v>75</v>
       </c>
       <c r="R33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="R33:R38" si="3">INT((S33-H33)/G33)+1</f>
         <v>4</v>
       </c>
       <c r="S33" s="1">
@@ -3167,7 +3182,7 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C34" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -3191,14 +3206,14 @@
         <v>10</v>
       </c>
       <c r="K34" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L34" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N34" s="1">
         <v>1</v>
@@ -3222,7 +3237,7 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C35" s="1">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -3246,14 +3261,14 @@
         <v>10</v>
       </c>
       <c r="K35" s="1">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L35" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N35" s="1">
         <v>1</v>
@@ -3276,37 +3291,193 @@
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:19">
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:19">
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:19">
-      <c r="E39" s="3"/>
+      <c r="C36" s="1">
+        <v>84</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="1">
+        <v>24</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>999</v>
+      </c>
+      <c r="J36" s="1">
+        <v>10</v>
+      </c>
+      <c r="K36" s="1">
+        <v>84</v>
+      </c>
+      <c r="L36" s="1">
+        <v>3</v>
+      </c>
+      <c r="M36" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1">
+        <v>3</v>
+      </c>
+      <c r="P36" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R36" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="S36" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C37" s="1">
+        <v>85</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="1">
+        <v>24</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>999</v>
+      </c>
+      <c r="J37" s="1">
+        <v>10</v>
+      </c>
+      <c r="K37" s="1">
+        <v>85</v>
+      </c>
+      <c r="L37" s="1">
+        <v>10</v>
+      </c>
+      <c r="M37" s="1">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N37" s="1">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1">
+        <v>3</v>
+      </c>
+      <c r="P37" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="R37" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="S37" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C38" s="1">
+        <v>86</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" s="1">
+        <v>24</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>999</v>
+      </c>
+      <c r="J38" s="1">
+        <v>10</v>
+      </c>
+      <c r="K38" s="1">
+        <v>86</v>
+      </c>
+      <c r="L38" s="1">
+        <v>10</v>
+      </c>
+      <c r="M38" s="1">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>3</v>
+      </c>
+      <c r="P38" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R38" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="S38" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="E39" s="6"/>
     </row>
     <row r="40" customHeight="1" spans="3:19">
-      <c r="E40" s="4"/>
+      <c r="E40" s="5"/>
     </row>
     <row r="41" customHeight="1" spans="3:19">
       <c r="E41" s="3"/>
     </row>
     <row r="42" customHeight="1" spans="3:19">
-      <c r="E42" s="4"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" customHeight="1" spans="3:19">
-      <c r="E43" s="5"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="44" customHeight="1" spans="3:19">
       <c r="E44" s="3"/>
     </row>
     <row r="45" customHeight="1" spans="3:19">
-      <c r="E45" s="3"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" customHeight="1" spans="3:19">
-      <c r="E46" s="3"/>
+      <c r="E46" s="5"/>
     </row>
     <row r="47" customHeight="1" spans="3:19">
       <c r="E47" s="3"/>
@@ -3315,22 +3486,22 @@
       <c r="E48" s="3"/>
     </row>
     <row r="49" customHeight="1" spans="5:5">
-      <c r="E49" s="5"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" customHeight="1" spans="5:5">
-      <c r="E50" s="6"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" customHeight="1" spans="5:5">
       <c r="E51" s="3"/>
     </row>
     <row r="52" customHeight="1" spans="5:5">
-      <c r="E52" s="6"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" customHeight="1" spans="5:5">
-      <c r="E53" s="3"/>
+      <c r="E53" s="6"/>
     </row>
     <row r="54" customHeight="1" spans="5:5">
-      <c r="E54" s="4"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" customHeight="1" spans="5:5">
       <c r="E55" s="6"/>
@@ -3339,28 +3510,28 @@
       <c r="E56" s="3"/>
     </row>
     <row r="57" customHeight="1" spans="5:5">
-      <c r="E57" s="3"/>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" customHeight="1" spans="5:5">
-      <c r="E58" s="3"/>
+      <c r="E58" s="6"/>
     </row>
     <row r="59" customHeight="1" spans="5:5">
-      <c r="E59" s="4"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" customHeight="1" spans="5:5">
       <c r="E60" s="3"/>
     </row>
     <row r="61" customHeight="1" spans="5:5">
-      <c r="E61" s="5"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" customHeight="1" spans="5:5">
-      <c r="E62" s="3"/>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" customHeight="1" spans="5:5">
       <c r="E63" s="3"/>
     </row>
     <row r="64" customHeight="1" spans="5:5">
-      <c r="E64" s="3"/>
+      <c r="E64" s="5"/>
     </row>
     <row r="65" customHeight="1" spans="5:5">
       <c r="E65" s="3"/>
@@ -3369,7 +3540,7 @@
       <c r="E66" s="3"/>
     </row>
     <row r="67" customHeight="1" spans="5:5">
-      <c r="E67" s="5"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" customHeight="1" spans="5:5">
       <c r="E68" s="3"/>
@@ -3378,70 +3549,79 @@
       <c r="E69" s="3"/>
     </row>
     <row r="70" customHeight="1" spans="5:5">
-      <c r="E70" s="3"/>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" customHeight="1" spans="5:5">
-      <c r="E71" s="6"/>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" customHeight="1" spans="5:5">
       <c r="E72" s="3"/>
     </row>
     <row r="73" customHeight="1" spans="5:5">
-      <c r="E73" s="5"/>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" customHeight="1" spans="5:5">
-      <c r="E74" s="3"/>
+      <c r="E74" s="6"/>
     </row>
     <row r="75" customHeight="1" spans="5:5">
-      <c r="E75" s="4"/>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" customHeight="1" spans="5:5">
-      <c r="E76" s="3"/>
+      <c r="E76" s="5"/>
     </row>
     <row r="77" customHeight="1" spans="5:5">
       <c r="E77" s="3"/>
     </row>
     <row r="78" customHeight="1" spans="5:5">
-      <c r="E78" s="3"/>
+      <c r="E78" s="4"/>
     </row>
     <row r="79" customHeight="1" spans="5:5">
-      <c r="E79" s="5"/>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" customHeight="1" spans="5:5">
       <c r="E80" s="3"/>
     </row>
-    <row r="81" customHeight="1" spans="5:9">
+    <row r="81" customHeight="1" spans="5:5">
       <c r="E81" s="3"/>
     </row>
-    <row r="82" customHeight="1" spans="5:9">
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" customHeight="1" spans="5:9">
+    <row r="82" customHeight="1" spans="5:5">
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83" customHeight="1" spans="5:5">
       <c r="E83" s="3"/>
     </row>
-    <row r="84" customHeight="1" spans="5:9">
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="5:9">
-      <c r="E85" s="5"/>
-    </row>
-    <row r="94" customHeight="1" spans="5:9">
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-    </row>
-    <row r="95" customHeight="1" spans="5:9">
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-    </row>
-    <row r="114" customHeight="1" spans="6:17">
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="Q114" s="7"/>
-    </row>
-    <row r="115" customHeight="1" spans="6:17">
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="Q115" s="7"/>
+    <row r="84" customHeight="1" spans="5:5">
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" customHeight="1" spans="5:5">
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" customHeight="1" spans="5:5">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" customHeight="1" spans="5:5">
+      <c r="E87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="5:5">
+      <c r="E88" s="5"/>
+    </row>
+    <row r="97" customHeight="1" spans="8:9">
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customHeight="1" spans="8:9">
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+    </row>
+    <row r="117" customHeight="1" spans="6:17">
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="Q117" s="7"/>
+    </row>
+    <row r="118" customHeight="1" spans="6:17">
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
+      <c r="Q118" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3651,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -3666,16 +3846,16 @@
         <v>100</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -3684,7 +3864,7 @@
         <v>99</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ref="R6:R26" si="0">INT((S6-H6)/G6)+1</f>
@@ -3705,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -3720,16 +3900,16 @@
         <v>100</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
@@ -3738,7 +3918,7 @@
         <v>99</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="0"/>
@@ -3759,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -3774,16 +3954,16 @@
         <v>100</v>
       </c>
       <c r="K8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="O8" s="1">
         <v>1</v>
@@ -3792,7 +3972,7 @@
         <v>99</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="0"/>
@@ -3813,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G9" s="1">
         <v>36</v>
@@ -3828,16 +4008,16 @@
         <v>10</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
@@ -3846,7 +4026,7 @@
         <v>99</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" si="0"/>
@@ -3867,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G10" s="1">
         <v>36</v>
@@ -3882,16 +4062,16 @@
         <v>10</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
@@ -3900,7 +4080,7 @@
         <v>99</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="0"/>
@@ -3921,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G11" s="1">
         <v>24</v>
@@ -3936,16 +4116,16 @@
         <v>30</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -3954,7 +4134,7 @@
         <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="0"/>
@@ -3975,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G12" s="1">
         <v>24</v>
@@ -3990,16 +4170,16 @@
         <v>50</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O12" s="1">
         <v>4</v>
@@ -4008,7 +4188,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="0"/>
@@ -4029,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G13" s="1">
         <v>24</v>
@@ -4044,16 +4224,16 @@
         <v>50</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O13" s="1">
         <v>4</v>
@@ -4062,7 +4242,7 @@
         <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="0"/>
@@ -4083,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G14" s="1">
         <v>24</v>
@@ -4098,16 +4278,16 @@
         <v>25</v>
       </c>
       <c r="K14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="M14" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="N14" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O14" s="1">
         <v>4</v>
@@ -4116,7 +4296,7 @@
         <v>99</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="0"/>
@@ -4137,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G15" s="1">
         <v>24</v>
@@ -4152,16 +4332,16 @@
         <v>50</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -4170,7 +4350,7 @@
         <v>99</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="0"/>
@@ -4191,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G16" s="1">
         <v>24</v>
@@ -4206,16 +4386,16 @@
         <v>50</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O16" s="1">
         <v>1</v>
@@ -4224,7 +4404,7 @@
         <v>99</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="0"/>
@@ -4245,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -4260,16 +4440,16 @@
         <v>10</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
@@ -4278,7 +4458,7 @@
         <v>99</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" si="0"/>
@@ -4299,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G18" s="1">
         <v>9</v>
@@ -4314,16 +4494,16 @@
         <v>100</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O18" s="1">
         <v>4</v>
@@ -4332,7 +4512,7 @@
         <v>99</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" si="0"/>
@@ -4353,7 +4533,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G19" s="1">
         <v>9</v>
@@ -4368,16 +4548,16 @@
         <v>100</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O19" s="1">
         <v>4</v>
@@ -4386,7 +4566,7 @@
         <v>99</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" si="0"/>
@@ -4407,7 +4587,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -4422,16 +4602,16 @@
         <v>100</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -4440,7 +4620,7 @@
         <v>99</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" si="0"/>
@@ -4461,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G21" s="1">
         <v>24</v>
@@ -4476,16 +4656,16 @@
         <v>50</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O21" s="1">
         <v>6</v>
@@ -4494,7 +4674,7 @@
         <v>99</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" si="0"/>
@@ -4515,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="G22" s="1">
         <v>24</v>
@@ -4530,16 +4710,16 @@
         <v>50</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O22" s="1">
         <v>6</v>
@@ -4548,7 +4728,7 @@
         <v>99</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" si="0"/>
@@ -4569,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G23" s="1">
         <v>24</v>
@@ -4584,16 +4764,16 @@
         <v>50</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O23" s="1">
         <v>6</v>
@@ -4602,7 +4782,7 @@
         <v>99</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" si="0"/>
@@ -4623,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G24" s="1">
         <v>24</v>
@@ -4638,16 +4818,16 @@
         <v>50</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O24" s="1">
         <v>6</v>
@@ -4656,7 +4836,7 @@
         <v>99</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" si="0"/>
@@ -4692,16 +4872,16 @@
         <v>50</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O25" s="1">
         <v>6</v>
@@ -4710,7 +4890,7 @@
         <v>99</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" si="0"/>
@@ -4731,7 +4911,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G26" s="1">
         <v>24</v>
@@ -4746,16 +4926,16 @@
         <v>50</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O26" s="1">
         <v>6</v>
@@ -4764,7 +4944,7 @@
         <v>99</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" si="0"/>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -2812,7 +2812,7 @@
         <v>999</v>
       </c>
       <c r="J25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K25" s="1">
         <v>10004</v>
@@ -2867,7 +2867,7 @@
         <v>999</v>
       </c>
       <c r="J26" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K26" s="1">
         <v>10005</v>
@@ -2922,7 +2922,7 @@
         <v>999</v>
       </c>
       <c r="J27" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K27" s="1">
         <v>10006</v>
@@ -2977,7 +2977,7 @@
         <v>999</v>
       </c>
       <c r="J28" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K28" s="1">
         <v>10001</v>
@@ -3032,7 +3032,7 @@
         <v>999</v>
       </c>
       <c r="J29" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K29" s="1">
         <v>10002</v>
@@ -3087,7 +3087,7 @@
         <v>999</v>
       </c>
       <c r="J30" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K30" s="1">
         <v>10028</v>
